--- a/outputs/448-11.xlsx
+++ b/outputs/448-11.xlsx
@@ -1,103 +1,153 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="4"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="15360" windowHeight="7755" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="144525" fullCalcOnLoad="1"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+  <si>
+    <t xml:space="preserve"> Teacher ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header10</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="7">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
+  <fonts count="9">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <charset val="178"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="12"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="12"/>
       <name val="Arial"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF008080"/>
-      <sz val="12"/>
+      <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color theme="0" tint="-0.15"/>
       <name val="Arial"/>
       <family val="2"/>
-      <b val="1"/>
-      <color theme="0" tint="-0.1499984740745262"/>
-      <sz val="12"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="16"/>
       <name val="Arial"/>
       <family val="2"/>
-      <b val="1"/>
-      <sz val="16"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
-      <b val="1"/>
-      <sz val="12"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="12"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="5">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="1"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.1499984740745262"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="1"/>
+        <bgColor rgb="FF003300"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="0" tint="-0.15"/>
+        <bgColor rgb="FFC0C0C0"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -105,117 +155,141 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+  <cellXfs count="7">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFD9D9D9"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
     </indexedColors>
   </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -250,119 +324,55 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
                 <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
                 <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
                 <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
                 <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
                 <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
@@ -370,33 +380,24 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
                 <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
@@ -409,13 +410,7 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -425,15 +420,13 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
-            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
               </a:schemeClr>
@@ -441,7 +434,6 @@
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
               </a:schemeClr>
@@ -449,534 +441,487 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
-                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr codeName="Sheet1">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:J17"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.625" defaultRowHeight="18.95" customHeight="1"/>
+  <dimension ref="A1:J15"/>
+  <sheetFormatPr defaultColWidth="9.62890625" defaultRowHeight="18.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col width="16.125" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
-    <col width="11.125" customWidth="1" style="2" min="2" max="10"/>
-    <col width="9.625" customWidth="1" style="2" min="11" max="16384"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="2" style="1" width="11.13"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="11" style="1" width="9.63"/>
   </cols>
   <sheetData>
-    <row r="1" ht="41.25" customHeight="1"/>
-    <row r="2" ht="18.95" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Teacher ID</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Header2</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Header3</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Header4</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>Header5</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>Header6</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>Header7</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>Header8</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>Header9</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>Header10</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18.95" customHeight="1">
-      <c r="A3" s="5" t="n">
+    <row r="1" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="n">
         <v>135791121</v>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="H3" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="I3" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="J3" s="4" t="n">
+      <c r="J3" s="5" t="n">
         <v>16</v>
       </c>
     </row>
-    <row r="4" ht="18.95" customHeight="1">
-      <c r="A4" s="7" t="n">
+    <row r="4" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="n">
         <v>135791122</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="I4" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="J4" s="1" t="n">
         <v>17</v>
       </c>
     </row>
-    <row r="5" ht="18.95" customHeight="1">
-      <c r="A5" s="7" t="n">
+    <row r="5" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="n">
         <v>135791123</v>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="I5" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="J5" s="2" t="n">
+      <c r="J5" s="1" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="6" ht="18.95" customHeight="1">
-      <c r="A6" s="7" t="n">
+    <row r="6" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="n">
         <v>135791124</v>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="H6" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="I6" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="J6" s="1" t="n">
         <v>19</v>
       </c>
     </row>
-    <row r="7" ht="18.95" customHeight="1">
-      <c r="A7" s="7" t="n">
+    <row r="7" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="n">
         <v>135791125</v>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="H7" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="I7" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="J7" s="2" t="n">
+      <c r="J7" s="1" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="8" ht="18.95" customHeight="1">
-      <c r="A8" s="7" t="n">
+    <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="n">
         <v>135791126</v>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C8" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F8" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G8" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H8" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="I8" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="J8" s="2" t="n">
+      <c r="J8" s="1" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="9" ht="18.95" customHeight="1">
-      <c r="A9" s="7" t="n">
+    <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="n">
         <v>135791127</v>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B9" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="C9" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F9" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="G9" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="H9" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="I9" s="2" t="n">
+      <c r="I9" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="J9" s="2" t="n">
+      <c r="J9" s="1" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="10" ht="18.95" customHeight="1">
-      <c r="A10" s="7" t="n">
+    <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="n">
         <v>135791128</v>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C10" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D10" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="F10" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="G10" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="H10" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="I10" s="2" t="n">
+      <c r="I10" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="J10" s="2" t="n">
+      <c r="J10" s="1" t="n">
         <v>24</v>
       </c>
     </row>
-    <row r="11" ht="18.95" customHeight="1">
-      <c r="A11" s="7" t="n">
+    <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="n">
         <v>135791129</v>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B11" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="C11" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="D11" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="F11" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="G11" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="H11" s="2" t="n">
+      <c r="H11" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="I11" s="2" t="n">
+      <c r="I11" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="J11" s="2" t="n">
+      <c r="J11" s="1" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="12" ht="18.95" customHeight="1">
-      <c r="A12" s="5" t="n">
+    <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="n">
         <v>135791130</v>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C12" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F12" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G12" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="H12" s="4" t="n">
+      <c r="H12" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="I12" s="4" t="n">
+      <c r="I12" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="J12" s="4" t="n">
+      <c r="J12" s="1" t="n">
         <v>27</v>
       </c>
     </row>
-    <row r="13" ht="18.95" customHeight="1">
-      <c r="A13" s="7" t="n">
+    <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="n">
         <v>135791131</v>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B13" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="C13" s="2" t="n">
+      <c r="C13" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="D13" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="F13" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="G13" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="H13" s="2" t="n">
+      <c r="H13" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="I13" s="2" t="n">
+      <c r="I13" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="J13" s="2" t="n">
+      <c r="J13" s="1" t="n">
         <v>28</v>
       </c>
     </row>
-    <row r="14" ht="18.95" customHeight="1">
-      <c r="A14" s="7" t="n">
+    <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="n">
         <v>135791132</v>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B14" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="C14" s="2" t="n">
+      <c r="C14" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="D14" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E14" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="F14" s="2" t="n">
+      <c r="F14" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="G14" s="2" t="n">
+      <c r="G14" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="H14" s="2" t="n">
+      <c r="H14" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="I14" s="2" t="n">
+      <c r="I14" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="J14" s="2" t="n">
+      <c r="J14" s="1" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="15" ht="18.95" customHeight="1">
-      <c r="A15" s="7" t="n">
+    <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="n">
         <v>135791133</v>
       </c>
-      <c r="B15" s="2" t="n">
+      <c r="B15" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="C15" s="2" t="n">
+      <c r="C15" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="D15" s="2" t="n">
+      <c r="D15" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E15" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="F15" s="2" t="n">
+      <c r="F15" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="G15" s="2" t="n">
+      <c r="G15" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="H15" s="2" t="n">
+      <c r="H15" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="I15" s="2" t="n">
+      <c r="I15" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="J15" s="2" t="n">
+      <c r="J15" s="1" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="16" ht="18.95" customHeight="1">
-      <c r="A16" s="7" t="n"/>
-      <c r="B16" s="2" t="n"/>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="n"/>
-      <c r="F16" s="2" t="n"/>
-      <c r="G16" s="2" t="n"/>
-      <c r="H16" s="2" t="n"/>
-      <c r="I16" s="2" t="n"/>
-      <c r="J16" s="2" t="n"/>
-    </row>
-    <row r="17" ht="18.95" customHeight="1">
-      <c r="A17" s="2" t="n"/>
-      <c r="B17" s="2" t="n"/>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n"/>
-      <c r="E17" s="2" t="n"/>
-      <c r="F17" s="2" t="n"/>
-      <c r="G17" s="2" t="n"/>
-      <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="n"/>
-      <c r="J17" s="2" t="n"/>
-    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>